--- a/Data/Results/Paired/15-07-2026/PAIR_004_STRICT_Chennai_to_Pondicherry.xlsx
+++ b/Data/Results/Paired/15-07-2026/PAIR_004_STRICT_Chennai_to_Pondicherry.xlsx
@@ -74562,7 +74562,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>CAND_003</t>
+          <t>CAND_004</t>
         </is>
       </c>
     </row>
@@ -75062,7 +75062,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+          <t>COMMON_START_END_ANCHORS_FULL_INTERIOR</t>
         </is>
       </c>
     </row>
@@ -75098,7 +75098,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Continuous same-direction common route confirmed; shared start/end anchors and the hard cropped-distance tolerance are satisfied.</t>
+          <t>Common same-direction start and end anchors confirmed; the entire original cleaned telemetry section between those anchors is retained. Internal overlap/unmatched-gap metrics are audit-only, and the final cropped-distance check is satisfied.</t>
         </is>
       </c>
     </row>
@@ -75254,7 +75254,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>29-09-2026 12:15:10</t>
+          <t>06-10-2026 23:15:38</t>
         </is>
       </c>
     </row>
